--- a/out/LSTM_Base_repeat_5_000006.xlsx
+++ b/out/LSTM_Base_repeat_5_000006.xlsx
@@ -2534,7 +2534,7 @@
         <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>1.599521431067185</v>
+        <v>8.62785843586423</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>1.599521431067185</v>
+        <v>8.62785843586423</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>2.199521431067184</v>
+        <v>9.227858435864231</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>2.199521431067184</v>
+        <v>0.0804624974787484</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>2.199521431067184</v>
+        <v>0.0804624974787484</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6502,14 +6502,14 @@
       </c>
       <c r="IZ7" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>2.199521431067184</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.7318388020611866</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8092,14 +8092,14 @@
       </c>
       <c r="IZ9" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>2.199521431067184</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8887,14 +8887,14 @@
       </c>
       <c r="IZ10" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>2.199521431067184</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9682,14 +9682,14 @@
       </c>
       <c r="IZ11" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>2.199521431067184</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>1.599521431067185</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>1.599521431067185</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>2.199521431067184</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.7318388020611866</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>1.599521431067185</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>1.599521431067185</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>2.199521431067184</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>2.199521431067184</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18427,14 +18427,14 @@
       </c>
       <c r="IZ22" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>2.199521431067184</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.599521431067185</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>1.599521431067185</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>2.199521431067184</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>2.199521431067184</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>2.199521431067184</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>2.199521431067184</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.599521431067185</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>2.199521431067184</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>2.199521431067184</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>2.199521431067184</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.7318388020611866</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33532,14 +33532,14 @@
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.599521431067185</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34327,14 +34327,14 @@
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>2.199521431067184</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35122,14 +35122,14 @@
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>2.199521431067184</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>2.199521431067184</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC44" t="n">
-        <v>-0.0003524812174077378</v>
+        <v>-4.036279517633375e-05</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.4536705733070571</v>
+        <v>0.05195006150234709</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>2.199521431067184</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.9082001314514829</v>
+        <v>0.1039984375104874</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.104771279911376</v>
+        <v>-0.01199740451623276</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.3485468121782732</v>
+        <v>0.03991229419093812</v>
       </c>
     </row>
     <row r="47">
@@ -38302,17 +38302,17 @@
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA47" t="n">
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.3485468121782732</v>
+        <v>0.03991229419093812</v>
       </c>
     </row>
     <row r="48">
@@ -39097,17 +39097,17 @@
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="JA48" t="n">
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.3485468121782732</v>
+        <v>0.03985383340237522</v>
       </c>
     </row>
     <row r="49">
@@ -39888,21 +39888,21 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0</v>
+        <v>0.1796040234711458</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA49" t="n">
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.3485317954802432</v>
+        <v>0.399419839118378</v>
       </c>
     </row>
     <row r="50">
@@ -40683,21 +40683,21 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>-0.01401167223883736</v>
+        <v>0.0343652061752737</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
-          <t>StopLoss</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA50" t="n">
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.3345201232414057</v>
+        <v>0.2882839304288852</v>
       </c>
     </row>
     <row r="51">
@@ -41478,21 +41478,21 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0</v>
+        <v>0.06019413528315388</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>1.599521431067185</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.3342469069081559</v>
+        <v>0.3743237162471069</v>
       </c>
     </row>
     <row r="52">
@@ -42273,21 +42273,21 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0</v>
+        <v>0.03296449898149532</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>2.199521431067184</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.3760926754689342</v>
+        <v>0.380006695219364</v>
       </c>
     </row>
     <row r="53">
@@ -43068,21 +43068,21 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>-0.05517183111531224</v>
+        <v>0.01361462133948809</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
-          <t>StopLoss</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA53" t="n">
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.7318388020611866</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.2790314898409308</v>
+        <v>0.3742372758438992</v>
       </c>
     </row>
     <row r="54">
@@ -43863,21 +43863,21 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0</v>
+        <v>0.0169626498609169</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>2.199521431067184</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.2787186890098434</v>
+        <v>0.3945508274791141</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.05712431596843884</v>
+        <v>0.01021204948025571</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>2.199521431067184</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.3935230422492586</v>
+        <v>0.3980026232258966</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.1169384171590679</v>
+        <v>0.007763531111272499</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>2.199521431067184</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.5701304634817503</v>
+        <v>0.4033129624394879</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.04357433343770555</v>
+        <v>0.003431049445745289</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.7318388020611866</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.5401130252288999</v>
+        <v>0.4024060506027483</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.05530063578796669</v>
+        <v>0.002721510970127304</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.6070988409812452</v>
+        <v>0.4044170334317791</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.02727794601543762</v>
+        <v>0.001345799342184725</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>1.599521431067185</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.6062826309121125</v>
+        <v>0.4043879042595944</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.01729966690197992</v>
+        <v>0.0007804842013199761</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>1.599521431067185</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.6135762737645616</v>
+        <v>0.4046027680698263</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.008649864038354844</v>
+        <v>0.0003877421006599881</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.7318388020611866</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.6135550030608556</v>
+        <v>0.4045972790793989</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.004244826917202777</v>
+        <v>0.0001904760750419558</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.6133865642670456</v>
+        <v>0.4045873307989093</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.00263986764183151</v>
+        <v>0.000108480194448693</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.6144180762712367</v>
+        <v>0.4046137122843436</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.0006959682562271265</v>
+        <v>3.294349193752244e-05</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.6131683272640396</v>
+        <v>0.4045710261632488</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.0003499925873620883</v>
+        <v>1.296632917816834e-05</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.6131703101628188</v>
+        <v>0.4045662388022761</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.0001999213318701714</v>
+        <v>4.784784520434025e-06</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.6132212623977908</v>
+        <v>0.4045630323505828</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>9.213956811491857e-05</v>
+        <v>-2.596391060734771e-07</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.6132053230906722</v>
+        <v>0.4045576458664252</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>6.243549451077907e-05</v>
+        <v>-2.090799254370459e-06</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.6132385127362867</v>
+        <v>0.4045542612479743</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>2.37104250774599e-05</v>
+        <v>-2.422504053549707e-06</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.6132214989913607</v>
+        <v>0.4045485938177006</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>1.277591828026595e-05</v>
+        <v>0</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.6132233154999766</v>
+        <v>0.4045489743527584</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>3.812596322305575e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.6132203545722701</v>
+        <v>0.4045492026737931</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>-4.140284059584509e-07</v>
+        <v>0</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.6132157961711439</v>
+        <v>0.404549292618443</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>-3.563918267525618e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.6132082193377216</v>
+        <v>0.4045484346848582</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>-3.335871218089884e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.6132036726731376</v>
+        <v>0.4045486630058929</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.6132028770089258</v>
+        <v>0.4045478673416811</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.6132029392782989</v>
+        <v>0.4045479296110542</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.6132029669535758</v>
+        <v>0.4045479572863311</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.6132031191675992</v>
+        <v>0.4045481095003544</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.6132027732266374</v>
+        <v>0.4045477635593926</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.613202849333649</v>
+        <v>0.4045478396664043</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.6132030153853106</v>
+        <v>0.4045480057180659</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.6132033751639107</v>
+        <v>0.404548365496666</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>2.199521431067184</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.6132033959203684</v>
+        <v>0.4045483862531236</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>2.199521431067184</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.6132034997026569</v>
+        <v>0.4045484900354122</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.7318388020611866</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.6132037280236916</v>
+        <v>0.4045487183564468</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.7318388020611866</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.6132036034849454</v>
+        <v>0.4045485938177006</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.6132036311602223</v>
+        <v>0.4045486214929775</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.6132036865107762</v>
+        <v>0.4045486768435314</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.6132039494259068</v>
+        <v>0.4045489397586621</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.6132038664000761</v>
+        <v>0.4045488567328314</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.6132036588354993</v>
+        <v>0.4045486491682546</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.6132036726731376</v>
+        <v>0.4045486630058929</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.6132038110495224</v>
+        <v>0.4045488013822776</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.6132035273779337</v>
+        <v>0.404548517710689</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.613203354407453</v>
+        <v>0.4045483447402082</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.6132032506251645</v>
+        <v>0.4045482409579197</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.6132033959203684</v>
+        <v>0.4045483862531236</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.6132036380790417</v>
+        <v>0.4045486284117969</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.6132034651085606</v>
+        <v>0.4045484554413159</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.6132031675993337</v>
+        <v>0.4045481579320889</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.6132031537616951</v>
+        <v>0.4045481440944504</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.6132027870642759</v>
+        <v>0.4045477773970312</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.6132027870642759</v>
+        <v>0.4045477773970312</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.6132027247949028</v>
+        <v>0.4045477151276581</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.6132026210126144</v>
+        <v>0.4045476113453696</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.6132024480421336</v>
+        <v>0.4045474383748888</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.6132024964738682</v>
+        <v>0.4045474868066234</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.6132021366952681</v>
+        <v>0.4045471270280234</v>
       </c>
     </row>
     <row r="109">
@@ -87588,21 +87588,21 @@
         <v>0</v>
       </c>
       <c r="IY109" t="n">
-        <v>-4.911469014191316e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ109" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA109" t="n">
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.6131970937686884</v>
+        <v>0.404547085515108</v>
       </c>
     </row>
     <row r="110">
@@ -88387,17 +88387,17 @@
       </c>
       <c r="IZ110" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA110" t="n">
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.6131970937686884</v>
+        <v>0.4045471408656617</v>
       </c>
     </row>
     <row r="111">
@@ -89182,17 +89182,17 @@
       </c>
       <c r="IZ111" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA111" t="n">
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.6131970937686884</v>
+        <v>0.4045471962162156</v>
       </c>
     </row>
     <row r="112">
@@ -89977,17 +89977,17 @@
       </c>
       <c r="IZ112" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA112" t="n">
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.6131970937686884</v>
+        <v>0.404547237729131</v>
       </c>
     </row>
     <row r="113">
@@ -90772,17 +90772,17 @@
       </c>
       <c r="IZ113" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA113" t="n">
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.6131970937686884</v>
+        <v>0.4045469678951809</v>
       </c>
     </row>
     <row r="114">
@@ -91567,17 +91567,17 @@
       </c>
       <c r="IZ114" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA114" t="n">
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.6131970937686884</v>
+        <v>0.4045470232457349</v>
       </c>
     </row>
     <row r="115">
@@ -92362,17 +92362,17 @@
       </c>
       <c r="IZ115" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA115" t="n">
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.6131970937686884</v>
+        <v>0.4045471685409388</v>
       </c>
     </row>
     <row r="116">
@@ -93157,17 +93157,17 @@
       </c>
       <c r="IZ116" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA116" t="n">
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.6131970937686884</v>
+        <v>0.4045471339468425</v>
       </c>
     </row>
     <row r="117">
@@ -93952,17 +93952,17 @@
       </c>
       <c r="IZ117" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA117" t="n">
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.6131970937686884</v>
+        <v>0.404547120109204</v>
       </c>
     </row>
     <row r="118">
@@ -94747,17 +94747,17 @@
       </c>
       <c r="IZ118" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>2.199521431067184</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.6126950115362326</v>
+        <v>0.4045472100538541</v>
       </c>
     </row>
     <row r="119">
@@ -95538,7 +95538,7 @@
         <v>0</v>
       </c>
       <c r="IY119" t="n">
-        <v>0.1217377369577275</v>
+        <v>0</v>
       </c>
       <c r="IZ119" t="inlineStr">
         <is>
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>2.199521431067184</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.857107938396567</v>
+        <v>0.4045475283195388</v>
       </c>
     </row>
     <row r="120">
@@ -96333,7 +96333,7 @@
         <v>0</v>
       </c>
       <c r="IY120" t="n">
-        <v>0.02625188649444911</v>
+        <v>0</v>
       </c>
       <c r="IZ120" t="inlineStr">
         <is>
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>2.199521431067184</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.7873532237206464</v>
+        <v>0.4045473484302387</v>
       </c>
     </row>
     <row r="121">
@@ -97128,7 +97128,7 @@
         <v>0</v>
       </c>
       <c r="IY121" t="n">
-        <v>0.01712021039927242</v>
+        <v>0</v>
       </c>
       <c r="IZ121" t="inlineStr">
         <is>
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.7318388020611866</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.7951395180082861</v>
+        <v>0.4045473899431541</v>
       </c>
     </row>
     <row r="122">
@@ -97923,21 +97923,21 @@
         <v>0</v>
       </c>
       <c r="IY122" t="n">
-        <v>-0.0001582900652836617</v>
+        <v>0</v>
       </c>
       <c r="IZ122" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA122" t="n">
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.7318388020611866</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.7771034141749971</v>
+        <v>0.4045472031350348</v>
       </c>
     </row>
     <row r="123">
@@ -98718,21 +98718,21 @@
         <v>0</v>
       </c>
       <c r="IY123" t="n">
-        <v>0.004727553774812872</v>
+        <v>0</v>
       </c>
       <c r="IZ123" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA123" t="n">
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.7823741090972112</v>
+        <v>0.4045472723232272</v>
       </c>
     </row>
     <row r="124">
@@ -99517,17 +99517,17 @@
       </c>
       <c r="IZ124" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA124" t="n">
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.7823741090972112</v>
+        <v>0.4045470716774694</v>
       </c>
     </row>
     <row r="125">
@@ -100312,17 +100312,17 @@
       </c>
       <c r="IZ125" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA125" t="n">
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.7823741090972112</v>
+        <v>0.4045471131903848</v>
       </c>
     </row>
     <row r="126">
@@ -101103,21 +101103,21 @@
         <v>0</v>
       </c>
       <c r="IY126" t="n">
-        <v>0</v>
+        <v>-3.873712549958921e-06</v>
       </c>
       <c r="IZ126" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell (Force)</t>
         </is>
       </c>
       <c r="JA126" t="n">
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.7823741090972112</v>
+        <v>0.4045471408656617</v>
       </c>
     </row>
   </sheetData>

--- a/out/LSTM_Base_repeat_5_000006.xlsx
+++ b/out/LSTM_Base_repeat_5_000006.xlsx
@@ -2534,7 +2534,7 @@
         <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>1.599521431067185</v>
+        <v>1.262528981303212</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>1.599521431067185</v>
+        <v>1.262528981303212</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>2.199521431067184</v>
+        <v>1.462528981303212</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>2.199521431067184</v>
+        <v>1.462528981303212</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>2.199521431067184</v>
+        <v>1.462528981303212</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>2.199521431067184</v>
+        <v>0.7925037851595846</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7297,14 +7297,14 @@
       </c>
       <c r="IZ8" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA8" t="n">
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.7318388020611866</v>
+        <v>0.7925037851595848</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>1</v>
       </c>
       <c r="JB9" t="n">
-        <v>2.199521431067184</v>
+        <v>0.7925037851595848</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>2.199521431067184</v>
+        <v>1.462528981303212</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>1</v>
       </c>
       <c r="JB11" t="n">
-        <v>2.199521431067184</v>
+        <v>0.5925037851595847</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.07752141098404303</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.07752141098404303</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>1.599521431067185</v>
+        <v>0.5925037851595847</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>1</v>
       </c>
       <c r="JB15" t="n">
-        <v>1.599521431067185</v>
+        <v>1.262528981303212</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>2.199521431067184</v>
+        <v>0.7925037851595846</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA17" t="n">
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.7318388020611866</v>
+        <v>0.7925037851595848</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>1.599521431067185</v>
+        <v>0.5925037851595847</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>1.599521431067185</v>
+        <v>1.462528981303212</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>2.199521431067184</v>
+        <v>1.462528981303212</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>2.199521431067184</v>
+        <v>1.462528981303212</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>1</v>
       </c>
       <c r="JB22" t="n">
-        <v>2.199521431067184</v>
+        <v>0.7925037851595848</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.07752141098404303</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.07752141098404303</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.599521431067185</v>
+        <v>0.5925037851595847</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>1</v>
       </c>
       <c r="JB26" t="n">
-        <v>1.599521431067185</v>
+        <v>1.262528981303212</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>2.199521431067184</v>
+        <v>1.462528981303212</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>2.199521431067184</v>
+        <v>1.462528981303212</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>2.199521431067184</v>
+        <v>1.462528981303212</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>2.199521431067184</v>
+        <v>0.7925037851595846</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.0775214109840431</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.0775214109840431</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.599521431067185</v>
+        <v>0.5925037851595846</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>2.199521431067184</v>
+        <v>1.462528981303212</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>2.199521431067184</v>
+        <v>1.462528981303212</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>2.199521431067184</v>
+        <v>0.7925037851595846</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA39" t="n">
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.7318388020611866</v>
+        <v>0.1224785890159569</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.0775214109840431</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.599521431067185</v>
+        <v>0.5925037851595846</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>2.199521431067184</v>
+        <v>1.462528981303212</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>2.199521431067184</v>
+        <v>1.462528981303212</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>2.199521431067184</v>
+        <v>1.462528981303212</v>
       </c>
       <c r="JC44" t="n">
-        <v>-0.0003524812174077378</v>
+        <v>-0.0002678825071685715</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.4536705733070571</v>
+        <v>0.344785443306906</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>2.199521431067184</v>
+        <v>0.7925037851595846</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.9082001314514829</v>
+        <v>0.6902238084084317</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.104771279911376</v>
+        <v>-0.07962522786376905</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.0775214109840431</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.3485468121782732</v>
+        <v>0.2648923329359686</v>
       </c>
     </row>
     <row r="47">
@@ -38302,17 +38302,17 @@
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA47" t="n">
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.3485468121782732</v>
+        <v>0.2648923329359686</v>
       </c>
     </row>
     <row r="48">
@@ -39097,17 +39097,17 @@
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="JA48" t="n">
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.3485468121782732</v>
+        <v>0.2648455292971716</v>
       </c>
     </row>
     <row r="49">
@@ -39888,21 +39888,21 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0</v>
+        <v>0.1437909005756924</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA49" t="n">
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.3485317954802432</v>
+        <v>0.5527136517395521</v>
       </c>
     </row>
     <row r="50">
@@ -40683,21 +40683,21 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>-0.01401167223883736</v>
+        <v>0.02751270654235187</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
-          <t>StopLoss</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA50" t="n">
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.0775214109840431</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.3345201232414057</v>
+        <v>0.4637384539356569</v>
       </c>
     </row>
     <row r="51">
@@ -41478,21 +41478,21 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0</v>
+        <v>0.04819133229811804</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA51" t="n">
         <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>1.599521431067185</v>
+        <v>0.5925037851595846</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.3342469069081559</v>
+        <v>0.5326217743741057</v>
       </c>
     </row>
     <row r="52">
@@ -42273,21 +42273,21 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0</v>
+        <v>0.02639132727773907</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA52" t="n">
         <v>1</v>
       </c>
       <c r="JB52" t="n">
-        <v>2.199521431067184</v>
+        <v>0.7925037851595846</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.3760926754689342</v>
+        <v>0.5371715586148293</v>
       </c>
     </row>
     <row r="53">
@@ -43068,21 +43068,21 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>-0.05517183111531224</v>
+        <v>0.01089895942551059</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
-          <t>StopLoss</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA53" t="n">
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.7318388020611866</v>
+        <v>0.7925037851595846</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.2790314898409308</v>
+        <v>0.5325517241214397</v>
       </c>
     </row>
     <row r="54">
@@ -43863,21 +43863,21 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0</v>
+        <v>0.01358023274914058</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA54" t="n">
         <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>2.199521431067184</v>
+        <v>0.7925037851595846</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.2787186890098434</v>
+        <v>0.5488143000612467</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.05712431596843884</v>
+        <v>0.008175020070754047</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>2.199521431067184</v>
+        <v>1.462528981303212</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.3935230422492586</v>
+        <v>0.55157673476512</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.1169384171590679</v>
+        <v>0.006213058782635087</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>2.199521431067184</v>
+        <v>0.7925037851595846</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.5701304634817503</v>
+        <v>0.5558268345868034</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.04357433343770555</v>
+        <v>0.002746064565488019</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.7318388020611866</v>
+        <v>0.1224785890159569</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.5401130252288999</v>
+        <v>0.5550997210856948</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.05530063578796669</v>
+        <v>0.002176713218464495</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.07752141098404317</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.6070988409812452</v>
+        <v>0.556708814374313</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.02727794601543762</v>
+        <v>0.001078140954011085</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>1.599521431067185</v>
+        <v>0.5925037851595846</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.6062826309121125</v>
+        <v>0.5566844829965173</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.01729966690197992</v>
+        <v>0.0006233873610559808</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>1.599521431067185</v>
+        <v>0.5925037851595846</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.6135762737645616</v>
+        <v>0.5568554556867696</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.008649864038354844</v>
+        <v>0.0003091936805279904</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.7318388020611866</v>
+        <v>-0.07752141098404325</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.6135550030608556</v>
+        <v>0.5568500644944278</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.004244826917202777</v>
+        <v>0.0001502310007686119</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.6133865642670456</v>
+        <v>0.5568411003834723</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.00263986764183151</v>
+        <v>8.511662500337389e-05</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.6144180762712367</v>
+        <v>0.5568614845357354</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.0006959682562271265</v>
+        <v>2.624758159560671e-05</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.6131683272640396</v>
+        <v>0.5568254489065986</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.0003499925873620883</v>
+        <v>1.07205380308973e-05</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.6131703101628188</v>
+        <v>0.5568206228578138</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.0001999213318701714</v>
+        <v>2.338588390325519e-06</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.6132212623977908</v>
+        <v>0.556817018180483</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>9.213956811491857e-05</v>
+        <v>-2.596391060734771e-07</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.6132053230906722</v>
+        <v>0.5568117078033371</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>6.243549451077907e-05</v>
+        <v>-2.090799254370459e-06</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.6132385127362867</v>
+        <v>0.556807783516986</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>2.37104250774599e-05</v>
+        <v>0</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.6132214989913607</v>
+        <v>0.5568074514136628</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>1.277591828026595e-05</v>
+        <v>0</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.6132233154999766</v>
+        <v>0.5568078319487206</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>3.812596322305575e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.6132203545722701</v>
+        <v>0.5568080602697553</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>-4.140284059584509e-07</v>
+        <v>0</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.6132157961711439</v>
+        <v>0.5568081502144052</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>-3.563918267525618e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.6132082193377216</v>
+        <v>0.5568072922808204</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>-3.335871218089884e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.6132036726731376</v>
+        <v>0.5568075206018551</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.6132028770089258</v>
+        <v>0.5568067249376434</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.6132029392782989</v>
+        <v>0.5568067872070165</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.6132029669535758</v>
+        <v>0.5568068148822933</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.6132031191675992</v>
+        <v>0.5568069670963166</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.6132027732266374</v>
+        <v>0.5568066211553548</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.613202849333649</v>
+        <v>0.5568066972623665</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.6132030153853106</v>
+        <v>0.5568068633140282</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.331838802061187</v>
+        <v>0.1224785890159568</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.6132033751639107</v>
+        <v>0.5568072230926282</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>2.199521431067184</v>
+        <v>0.7925037851595845</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.6132033959203684</v>
+        <v>0.5568072438490859</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>2.199521431067184</v>
+        <v>0.7925037851595846</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.6132034997026569</v>
+        <v>0.5568073476313744</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.7318388020611866</v>
+        <v>0.1224785890159568</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.6132037280236916</v>
+        <v>0.556807575952409</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.7318388020611866</v>
+        <v>-0.5475466071276708</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.6132036034849454</v>
+        <v>0.5568074514136628</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.6132036311602223</v>
+        <v>0.5568074790889397</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.6132036865107762</v>
+        <v>0.5568075344394937</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.6132039494259068</v>
+        <v>0.5568077973546244</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.6132038664000761</v>
+        <v>0.5568077143287936</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.6132036588354993</v>
+        <v>0.5568075067642169</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.6132036726731376</v>
+        <v>0.5568075206018551</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.6132038110495224</v>
+        <v>0.5568076589782399</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.6132035273779337</v>
+        <v>0.5568073753066513</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.613203354407453</v>
+        <v>0.5568072023361704</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.6132032506251645</v>
+        <v>0.556807098553882</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.6132033959203684</v>
+        <v>0.5568072438490859</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.6132036380790417</v>
+        <v>0.5568074860077591</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.6132034651085606</v>
+        <v>0.5568073130372782</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.6132031675993337</v>
+        <v>0.5568070155280512</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.6132031537616951</v>
+        <v>0.5568070016904126</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.6132027870642759</v>
+        <v>0.5568066349929934</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.6132027870642759</v>
+        <v>0.5568066349929934</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.6132027247949028</v>
+        <v>0.5568065727236203</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.6132026210126144</v>
+        <v>0.5568064689413318</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.6132024480421336</v>
+        <v>0.5568062959708511</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.6132024964738682</v>
+        <v>0.5568063444025857</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.6132021366952681</v>
+        <v>0.5568059846239856</v>
       </c>
     </row>
     <row r="109">
@@ -87588,21 +87588,21 @@
         <v>0</v>
       </c>
       <c r="IY109" t="n">
-        <v>-4.911469014191316e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ109" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA109" t="n">
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.6131970937686884</v>
+        <v>0.5568059431110702</v>
       </c>
     </row>
     <row r="110">
@@ -88387,17 +88387,17 @@
       </c>
       <c r="IZ110" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA110" t="n">
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.6131970937686884</v>
+        <v>0.5568059984616239</v>
       </c>
     </row>
     <row r="111">
@@ -89182,17 +89182,17 @@
       </c>
       <c r="IZ111" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA111" t="n">
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.6131970937686884</v>
+        <v>0.5568060538121778</v>
       </c>
     </row>
     <row r="112">
@@ -89977,17 +89977,17 @@
       </c>
       <c r="IZ112" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA112" t="n">
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.6131970937686884</v>
+        <v>0.5568060953250933</v>
       </c>
     </row>
     <row r="113">
@@ -90772,17 +90772,17 @@
       </c>
       <c r="IZ113" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA113" t="n">
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.6131970937686884</v>
+        <v>0.5568058254911431</v>
       </c>
     </row>
     <row r="114">
@@ -91567,17 +91567,17 @@
       </c>
       <c r="IZ114" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA114" t="n">
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.6131970937686884</v>
+        <v>0.5568058808416971</v>
       </c>
     </row>
     <row r="115">
@@ -92362,17 +92362,17 @@
       </c>
       <c r="IZ115" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA115" t="n">
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.6131970937686884</v>
+        <v>0.556806026136901</v>
       </c>
     </row>
     <row r="116">
@@ -93157,17 +93157,17 @@
       </c>
       <c r="IZ116" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA116" t="n">
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.6131970937686884</v>
+        <v>0.5568059915428047</v>
       </c>
     </row>
     <row r="117">
@@ -93952,17 +93952,17 @@
       </c>
       <c r="IZ117" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA117" t="n">
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.331838802061187</v>
+        <v>0.1224785890159568</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.6131970937686884</v>
+        <v>0.5568059777051662</v>
       </c>
     </row>
     <row r="118">
@@ -94747,17 +94747,17 @@
       </c>
       <c r="IZ118" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA118" t="n">
         <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>2.199521431067184</v>
+        <v>0.7925037851595845</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.6126950115362326</v>
+        <v>0.5568060676498164</v>
       </c>
     </row>
     <row r="119">
@@ -95538,7 +95538,7 @@
         <v>0</v>
       </c>
       <c r="IY119" t="n">
-        <v>0.1217377369577275</v>
+        <v>0</v>
       </c>
       <c r="IZ119" t="inlineStr">
         <is>
@@ -95549,10 +95549,10 @@
         <v>1</v>
       </c>
       <c r="JB119" t="n">
-        <v>2.199521431067184</v>
+        <v>1.462528981303212</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.857107938396567</v>
+        <v>0.556806385915501</v>
       </c>
     </row>
     <row r="120">
@@ -96333,7 +96333,7 @@
         <v>0</v>
       </c>
       <c r="IY120" t="n">
-        <v>0.02625188649444911</v>
+        <v>0</v>
       </c>
       <c r="IZ120" t="inlineStr">
         <is>
@@ -96344,10 +96344,10 @@
         <v>1</v>
       </c>
       <c r="JB120" t="n">
-        <v>2.199521431067184</v>
+        <v>0.7925037851595845</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.7873532237206464</v>
+        <v>0.5568062060262009</v>
       </c>
     </row>
     <row r="121">
@@ -97128,7 +97128,7 @@
         <v>0</v>
       </c>
       <c r="IY121" t="n">
-        <v>0.01712021039927242</v>
+        <v>0</v>
       </c>
       <c r="IZ121" t="inlineStr">
         <is>
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.7318388020611866</v>
+        <v>0.1224785890159567</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.7951395180082861</v>
+        <v>0.5568062475391163</v>
       </c>
     </row>
     <row r="122">
@@ -97923,21 +97923,21 @@
         <v>0</v>
       </c>
       <c r="IY122" t="n">
-        <v>-0.0001582900652836617</v>
+        <v>0</v>
       </c>
       <c r="IZ122" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA122" t="n">
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.7318388020611866</v>
+        <v>-0.5475466071276708</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.7771034141749971</v>
+        <v>0.556806060730997</v>
       </c>
     </row>
     <row r="123">
@@ -98718,21 +98718,21 @@
         <v>0</v>
       </c>
       <c r="IY123" t="n">
-        <v>0.004727553774812872</v>
+        <v>0</v>
       </c>
       <c r="IZ123" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA123" t="n">
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.7823741090972112</v>
+        <v>0.5568061299191895</v>
       </c>
     </row>
     <row r="124">
@@ -99517,17 +99517,17 @@
       </c>
       <c r="IZ124" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA124" t="n">
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.7823741090972112</v>
+        <v>0.5568059292734316</v>
       </c>
     </row>
     <row r="125">
@@ -100312,17 +100312,17 @@
       </c>
       <c r="IZ125" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA125" t="n">
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.7823741090972112</v>
+        <v>0.5568059707863471</v>
       </c>
     </row>
     <row r="126">
@@ -101103,21 +101103,21 @@
         <v>0</v>
       </c>
       <c r="IY126" t="n">
-        <v>0</v>
+        <v>-3.873712549958921e-06</v>
       </c>
       <c r="IZ126" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell (Force)</t>
         </is>
       </c>
       <c r="JA126" t="n">
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.331838802061187</v>
+        <v>-0.7475466071276708</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.7823741090972112</v>
+        <v>0.5568059984616239</v>
       </c>
     </row>
   </sheetData>

--- a/out/LSTM_Base_repeat_5_000006.xlsx
+++ b/out/LSTM_Base_repeat_5_000006.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>1</v>
+        <v>0.02401808835566044</v>
       </c>
       <c r="JB2" t="n">
-        <v>1.262528981303212</v>
+        <v>-0.3</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>1</v>
+        <v>0.01093730516731739</v>
       </c>
       <c r="JB3" t="n">
-        <v>1.262528981303212</v>
+        <v>-0.3</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0.004527732729911804</v>
       </c>
       <c r="JB4" t="n">
-        <v>1.462528981303212</v>
+        <v>-0.3</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0.002661991864442825</v>
       </c>
       <c r="JB5" t="n">
-        <v>1.462528981303212</v>
+        <v>-0.3</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5707,14 +5707,14 @@
       </c>
       <c r="IZ6" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>1</v>
+        <v>0.0004144348204135895</v>
       </c>
       <c r="JB6" t="n">
-        <v>1.462528981303212</v>
+        <v>-0.3</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6502,14 +6502,14 @@
       </c>
       <c r="IZ7" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>1</v>
+        <v>0.0003145709633827209</v>
       </c>
       <c r="JB7" t="n">
-        <v>0.7925037851595846</v>
+        <v>-0.3</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7297,14 +7297,14 @@
       </c>
       <c r="IZ8" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>-0.0008414164185523987</v>
       </c>
       <c r="JB8" t="n">
-        <v>0.7925037851595848</v>
+        <v>-0.3</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8092,14 +8092,14 @@
       </c>
       <c r="IZ9" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>1</v>
+        <v>0.000625070184469223</v>
       </c>
       <c r="JB9" t="n">
-        <v>0.7925037851595848</v>
+        <v>-0.3</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8887,14 +8887,14 @@
       </c>
       <c r="IZ10" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0.001454573124647141</v>
       </c>
       <c r="JB10" t="n">
-        <v>1.462528981303212</v>
+        <v>-0.3</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9682,14 +9682,14 @@
       </c>
       <c r="IZ11" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>1</v>
+        <v>0.0001767165958881378</v>
       </c>
       <c r="JB11" t="n">
-        <v>0.5925037851595847</v>
+        <v>-0.3</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>-0.001016266644001007</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.07752141098404303</v>
+        <v>-0.3</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>-0.001452021300792694</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.07752141098404303</v>
+        <v>-0.3</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0.0004014559090137482</v>
       </c>
       <c r="JB14" t="n">
-        <v>0.5925037851595847</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0.0004837177693843842</v>
       </c>
       <c r="JB15" t="n">
-        <v>1.262528981303212</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>2.967193722724915e-05</v>
       </c>
       <c r="JB16" t="n">
-        <v>0.7925037851595846</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0</v>
+        <v>-0.0002847388386726379</v>
       </c>
       <c r="JB17" t="n">
-        <v>0.7925037851595848</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0.000710759311914444</v>
       </c>
       <c r="JB18" t="n">
-        <v>0.5925037851595847</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0.002036813646554947</v>
       </c>
       <c r="JB19" t="n">
-        <v>1.462528981303212</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0.003661461174488068</v>
       </c>
       <c r="JB20" t="n">
-        <v>1.462528981303212</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0.002424430102109909</v>
       </c>
       <c r="JB21" t="n">
-        <v>1.462528981303212</v>
+        <v>0.16</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0.0006638504564762115</v>
       </c>
       <c r="JB22" t="n">
-        <v>0.7925037851595848</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0</v>
+        <v>-0.000803433358669281</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.07752141098404303</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>-0.0009487234055995941</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.07752141098404303</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0.001449402421712875</v>
       </c>
       <c r="JB25" t="n">
-        <v>0.5925037851595847</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0.0009333454072475433</v>
       </c>
       <c r="JB26" t="n">
-        <v>1.262528981303212</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0.003189105540513992</v>
       </c>
       <c r="JB27" t="n">
-        <v>1.462528981303212</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0.008544333279132843</v>
       </c>
       <c r="JB28" t="n">
-        <v>1.462528981303212</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0.005529202520847321</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.462528981303212</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0.0008239597082138062</v>
       </c>
       <c r="JB30" t="n">
-        <v>0.7925037851595846</v>
+        <v>0.16</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>-0.0009934194386005402</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.0775214109840431</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>-0.002373509109020233</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.7475466071276708</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>-0.002976935356855392</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.7475466071276708</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>-0.001772891730070114</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.0775214109840431</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0.002782799303531647</v>
       </c>
       <c r="JB35" t="n">
-        <v>0.5925037851595846</v>
+        <v>-0.3</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0.00232696533203125</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.462528981303212</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0.001132678240537643</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.462528981303212</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0.001361511647701263</v>
       </c>
       <c r="JB38" t="n">
-        <v>0.7925037851595846</v>
+        <v>0.3</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0</v>
+        <v>-6.862729787826538e-05</v>
       </c>
       <c r="JB39" t="n">
-        <v>0.1224785890159569</v>
+        <v>0.16</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0</v>
+        <v>-0.0002135485410690308</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.0775214109840431</v>
+        <v>0.3</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0.0009385310113430023</v>
       </c>
       <c r="JB41" t="n">
-        <v>0.5925037851595846</v>
+        <v>0.3</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.003533128648996353</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.462528981303212</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.006077051162719727</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.462528981303212</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.01085365936160088</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.462528981303212</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC44" t="n">
-        <v>-0.0002678825071685715</v>
+        <v>-0.0001826481971237809</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.344785443306906</v>
+        <v>0.2350824573080914</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.008735669776797295</v>
       </c>
       <c r="JB45" t="n">
-        <v>0.7925037851595846</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.6902238084084317</v>
+        <v>0.4706098037066381</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.07962522786376905</v>
+        <v>-0.05429020204081502</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>-0.00134715810418129</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.0775214109840431</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.2648923329359686</v>
+        <v>0.1806096070701526</v>
       </c>
     </row>
     <row r="47">
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0</v>
+        <v>-0.004227537661790848</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.7475466071276708</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.2648923329359686</v>
+        <v>0.1806096070701526</v>
       </c>
     </row>
     <row r="48">
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>-0.0035698302090168</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.7475466071276708</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.2648455292971716</v>
+        <v>0.1805910395481882</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.1437909005756924</v>
+        <v>0.0570434430597642</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>-0.004633154720067978</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.7475466071276708</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.5527136517395521</v>
+        <v>0.2947915124954945</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.02751270654235187</v>
+        <v>0.01091462008372666</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>-0.0007466115057468414</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.0775214109840431</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.4637384539356569</v>
+        <v>0.259494065861634</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.04819133229811804</v>
+        <v>0.01911799219836324</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0.000262729823589325</v>
       </c>
       <c r="JB51" t="n">
-        <v>0.5925037851595846</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.5326217743741057</v>
+        <v>0.2868207804374635</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.02639132727773907</v>
+        <v>0.01046855120193331</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>7.447600364685059e-05</v>
       </c>
       <c r="JB52" t="n">
-        <v>0.7925037851595846</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.5371715586148293</v>
+        <v>0.2886245691298491</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.01089895942551059</v>
+        <v>0.004320592946778152</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>-0.002295538783073425</v>
       </c>
       <c r="JB53" t="n">
-        <v>0.7925037851595846</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.5325517241214397</v>
+        <v>0.2867888174798759</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.01358023274914058</v>
+        <v>0.005384548135998066</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0.004057969897985458</v>
       </c>
       <c r="JB54" t="n">
-        <v>0.7925037851595846</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.5488143000612467</v>
+        <v>0.2932375076891319</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.008175020070754047</v>
+        <v>0.003239595567570506</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0.0007862113416194916</v>
       </c>
       <c r="JB55" t="n">
-        <v>1.462528981303212</v>
+        <v>0.16</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.55157673476512</v>
+        <v>0.2943304081322081</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.006213058782635087</v>
+        <v>0.002461742186812474</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0.006167419254779816</v>
       </c>
       <c r="JB56" t="n">
-        <v>0.7925037851595846</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.5558268345868034</v>
+        <v>0.2960138039118054</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.002746064565488019</v>
+        <v>0.001086843649041172</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>-0.004535634070634842</v>
       </c>
       <c r="JB57" t="n">
-        <v>0.1224785890159569</v>
+        <v>0.16</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.5550997210856948</v>
+        <v>0.2957222112051263</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.002176713218464495</v>
+        <v>0.0008601186519460365</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0</v>
+        <v>-0.008574586361646652</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.07752141098404317</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.556708814374313</v>
+        <v>0.2963578141729729</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.001078140954011085</v>
+        <v>0.0004252546052884681</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0.007759511470794678</v>
       </c>
       <c r="JB59" t="n">
-        <v>0.5925037851595846</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.5566844829965173</v>
+        <v>0.2963451351961116</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.0006233873610559808</v>
+        <v>0.0002451912641241405</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>0.009618697687983513</v>
       </c>
       <c r="JB60" t="n">
-        <v>0.5925037851595846</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.5568554556867696</v>
+        <v>0.2964100358686715</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.0003091936805279904</v>
+        <v>0.0001200956320620703</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>-0.003260556608438492</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.07752141098404325</v>
+        <v>0.16</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.5568500644944278</v>
+        <v>0.2964048801161652</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.0001502310007686119</v>
+        <v>5.536761141001575e-05</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>-0.0103844441473484</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.7475466071276708</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.5568411003834723</v>
+        <v>0.2963983173766236</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>8.511662500337389e-05</v>
+        <v>3.17141805569301e-05</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>-0.01274488866329193</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.7475466071276708</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.5568614845357354</v>
+        <v>0.2964034702101466</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>2.624758159560671e-05</v>
+        <v>6.159850569859539e-06</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>-0.01843415945768356</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.7475466071276708</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.5568254489065986</v>
+        <v>0.2963862790458063</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>1.07205380308973e-05</v>
+        <v>1.73737344181313e-06</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0</v>
+        <v>-0.01833918690681458</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.7475466071276708</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.5568206228578138</v>
+        <v>0.2963813535963271</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>2.338588390325519e-06</v>
+        <v>-2.553803869891494e-06</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0</v>
+        <v>-0.01742067560553551</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.7475466071276708</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.556817018180483</v>
+        <v>0.2963769524677221</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>-2.596391060734771e-07</v>
+        <v>-2.629819553036738e-06</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0</v>
+        <v>-0.01191714033484459</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.7475466071276708</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.5568117078033371</v>
+        <v>0.2963717972791493</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>-2.090799254370459e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>-0.007739510387182236</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.7475466071276708</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.556807783516986</v>
+        <v>0.2963723369470495</v>
       </c>
     </row>
     <row r="69">
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>-0.007139947265386581</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.7475466071276708</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.5568074514136628</v>
+        <v>0.2963720048437263</v>
       </c>
     </row>
     <row r="70">
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>-0.004889179021120071</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.7475466071276708</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.5568078319487206</v>
+        <v>0.296372385378784</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>-0.008217871189117432</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.7475466071276708</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.5568080602697553</v>
+        <v>0.2963726136998187</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>-0.01077405735850334</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.7475466071276708</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.5568081502144052</v>
+        <v>0.2963727036444687</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>-0.0124669037759304</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.7475466071276708</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.5568072922808204</v>
+        <v>0.2963718457108839</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>-0.01185760274529457</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.7475466071276708</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.5568075206018551</v>
+        <v>0.2963720740319186</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>-0.01110270991921425</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.7475466071276708</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.5568067249376434</v>
+        <v>0.2963712783677068</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>-0.01288390904664993</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.7475466071276708</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.5568067872070165</v>
+        <v>0.2963713406370799</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>-0.01137342676520348</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.7475466071276708</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.5568068148822933</v>
+        <v>0.2963713683123568</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>-0.007614646106958389</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.7475466071276708</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.5568069670963166</v>
+        <v>0.2963715205263801</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>-0.008462987840175629</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.7475466071276708</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.5568066211553548</v>
+        <v>0.2963711745854183</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>-0.007326971739530563</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.7475466071276708</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.5568066972623665</v>
+        <v>0.29637125069243</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>-0.007719103246927261</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.7475466071276708</v>
+        <v>0.16</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.5568068633140282</v>
+        <v>0.2963714167440916</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>-0.002736635506153107</v>
       </c>
       <c r="JB82" t="n">
-        <v>0.1224785890159568</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.5568072230926282</v>
+        <v>0.2963717765226916</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>4.751607775688171e-05</v>
       </c>
       <c r="JB83" t="n">
-        <v>0.7925037851595845</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.5568072438490859</v>
+        <v>0.2963717972791493</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0.001168988645076752</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.7925037851595846</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.5568073476313744</v>
+        <v>0.2963719010614378</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>-0.003490444272756577</v>
       </c>
       <c r="JB85" t="n">
-        <v>0.1224785890159568</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.556807575952409</v>
+        <v>0.2963721293824725</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>-0.007341720163822174</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.5475466071276708</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.5568074514136628</v>
+        <v>0.2963720048437263</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>-0.009060382843017578</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.7475466071276708</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.5568074790889397</v>
+        <v>0.2963720325190031</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0</v>
+        <v>-0.004624165594577789</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.7475466071276708</v>
+        <v>0.3</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.5568075344394937</v>
+        <v>0.2963720878695571</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>-0.005427982658147812</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.7475466071276708</v>
+        <v>-0.3</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.5568077973546244</v>
+        <v>0.2963723507846878</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>-0.006143849343061447</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.7475466071276708</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.5568077143287936</v>
+        <v>0.296372267758857</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>-0.00680243968963623</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.7475466071276708</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.5568075067642169</v>
+        <v>0.2963720601942803</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>-0.006603997200727463</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.7475466071276708</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.5568075206018551</v>
+        <v>0.2963720740319186</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>-0.006434950977563858</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.7475466071276708</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.5568076589782399</v>
+        <v>0.2963722124083033</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0</v>
+        <v>-0.007104396820068359</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.7475466071276708</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.5568073753066513</v>
+        <v>0.2963719287367146</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>-0.007763873785734177</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.7475466071276708</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.5568072023361704</v>
+        <v>0.2963717557662339</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>-0.004714358597993851</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.7475466071276708</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.556807098553882</v>
+        <v>0.2963716519839454</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>-0.003612272441387177</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.7475466071276708</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.5568072438490859</v>
+        <v>0.2963717972791493</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>-0.003910336643457413</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.7475466071276708</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.5568074860077591</v>
+        <v>0.2963720394378225</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>-0.005174364894628525</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.7475466071276708</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.5568073130372782</v>
+        <v>0.2963718664673415</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>-0.006349757313728333</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.7475466071276708</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.5568070155280512</v>
+        <v>0.2963715689581146</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>-0.006625670939683914</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.7475466071276708</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.5568070016904126</v>
+        <v>0.2963715551204761</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>-0.006951596587896347</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.7475466071276708</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.5568066349929934</v>
+        <v>0.2963711884230569</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>-0.004981637001037598</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.7475466071276708</v>
+        <v>-0.16</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.5568066349929934</v>
+        <v>0.2963711884230569</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>-0.003291178494691849</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.7475466071276708</v>
+        <v>-0.3</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.5568065727236203</v>
+        <v>0.2963711261536838</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>-0.005723625421524048</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.7475466071276708</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.5568064689413318</v>
+        <v>0.2963710223713952</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>-0.006453823298215866</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.7475466071276708</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.5568062959708511</v>
+        <v>0.2963708494009145</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>-0.006226107478141785</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.7475466071276708</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.5568063444025857</v>
+        <v>0.2963708978326491</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>-0.006747033447027206</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.7475466071276708</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.5568059846239856</v>
+        <v>0.296370538054049</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>-0.006300240755081177</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.7475466071276708</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.5568059431110702</v>
+        <v>0.2963704965411336</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>-0.004019137471914291</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.7475466071276708</v>
+        <v>-0.16</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.5568059984616239</v>
+        <v>0.2963705518916873</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>-0.004074264317750931</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.7475466071276708</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.5568060538121778</v>
+        <v>0.2963706072422413</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>-0.003978490829467773</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.7475466071276708</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.5568060953250933</v>
+        <v>0.2963706487551567</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>-0.004183609038591385</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.7475466071276708</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.5568058254911431</v>
+        <v>0.2963703789212066</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>-0.003098469227552414</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.7475466071276708</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.5568058808416971</v>
+        <v>0.2963704342717605</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>-0.002578463405370712</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.7475466071276708</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.556806026136901</v>
+        <v>0.2963705795669644</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>-0.002031818032264709</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.7475466071276708</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.5568059915428047</v>
+        <v>0.2963705449728682</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>-0.002291828393936157</v>
       </c>
       <c r="JB117" t="n">
-        <v>0.1224785890159568</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.5568059777051662</v>
+        <v>0.2963705311352297</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0.001099471002817154</v>
       </c>
       <c r="JB118" t="n">
-        <v>0.7925037851595845</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.5568060676498164</v>
+        <v>0.2963706210798798</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0.006404697895050049</v>
       </c>
       <c r="JB119" t="n">
-        <v>1.462528981303212</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.556806385915501</v>
+        <v>0.2963709393455645</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>1</v>
+        <v>0.001004558056592941</v>
       </c>
       <c r="JB120" t="n">
-        <v>0.7925037851595845</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.5568062060262009</v>
+        <v>0.2963707594562643</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>-0.003801975399255753</v>
       </c>
       <c r="JB121" t="n">
-        <v>0.1224785890159567</v>
+        <v>-0.3</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.5568062475391163</v>
+        <v>0.2963708009691797</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>-0.005642373114824295</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.5475466071276708</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.556806060730997</v>
+        <v>0.2963706141610604</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>-0.007034983485937119</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.7475466071276708</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.5568061299191895</v>
+        <v>0.2963706833492529</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>-0.006254635751247406</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.7475466071276708</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.5568059292734316</v>
+        <v>0.2963704827034951</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>-0.005653407424688339</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.7475466071276708</v>
+        <v>-0.4399999999999996</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.5568059707863471</v>
+        <v>0.2963705242164105</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>-0.003683753311634064</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.7475466071276708</v>
+        <v>-0.1599999999999997</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.5568059984616239</v>
+        <v>0.2963705518916873</v>
       </c>
     </row>
   </sheetData>

--- a/out/LSTM_Base_repeat_5_000006.xlsx
+++ b/out/LSTM_Base_repeat_5_000006.xlsx
@@ -14459,7 +14459,7 @@
         <v>-0.0002847388386726379</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.7199999999999999</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0.000710759311914444</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.5799999999999998</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0.002036813646554947</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.4399999999999999</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0.003661461174488068</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.4399999999999999</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA21" t="n">
         <v>0.002424430102109909</v>
       </c>
       <c r="JB21" t="n">
-        <v>0.16</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
